--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig8_veto_cooldown_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig8_veto_cooldown_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.363962202671879</v>
+        <v>3.877484522645813</v>
       </c>
       <c r="C3" t="n">
-        <v>1.026392961876833</v>
+        <v>0.7983056370153144</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9286412512218964</v>
+        <v>0.04887585532746823</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3421309872922776</v>
+        <v>0.1466275659824047</v>
       </c>
       <c r="F3" t="n">
         <v>0.3910068426197458</v>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.154447702834799</v>
+        <v>0.8634734441186055</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4072987943955687</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -679,19 +679,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.058325187357445</v>
+        <v>2.981427174975562</v>
       </c>
       <c r="C8" t="n">
         <v>1.058976865428478</v>
       </c>
       <c r="D8" t="n">
-        <v>1.775822743564679</v>
+        <v>5.897686542847834</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7168458781362007</v>
+        <v>1.971326164874552</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5050505050505051</v>
+        <v>0.6679700228087325</v>
       </c>
       <c r="G8" t="n">
         <v>0.1955034213098729</v>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.88139459107201</v>
+        <v>1.726946888237211</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4887585532746823</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -769,13 +769,13 @@
         <v>0.8308895405669598</v>
       </c>
       <c r="D11" t="n">
-        <v>5.848810687520365</v>
+        <v>8.031932225480611</v>
       </c>
       <c r="E11" t="n">
-        <v>1.955034213098729</v>
+        <v>1.319648093841642</v>
       </c>
       <c r="F11" t="n">
-        <v>1.221896383186706</v>
+        <v>1.01010101010101</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.28022157054415</v>
+        <v>3.372434017595308</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9612251547735419</v>
+        <v>0.4235907461713913</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4235907461713913</v>
+        <v>0.4072987943955687</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2932551319648094</v>
+        <v>0.3095470837406321</v>
       </c>
       <c r="F12" t="n">
-        <v>0.570218312153796</v>
+        <v>0.4398826979472141</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.899967416096449</v>
+        <v>2.117953730856957</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7494297816878462</v>
+        <v>0.570218312153796</v>
       </c>
       <c r="D14" t="n">
         <v>0.04887585532746823</v>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig8_veto_cooldown_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig8_veto_cooldown_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -769,10 +769,10 @@
         <v>0.8308895405669598</v>
       </c>
       <c r="D11" t="n">
-        <v>8.031932225480611</v>
+        <v>7.917888563049853</v>
       </c>
       <c r="E11" t="n">
-        <v>1.319648093841642</v>
+        <v>1.417399804496579</v>
       </c>
       <c r="F11" t="n">
         <v>1.01010101010101</v>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig8_veto_cooldown_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig8_veto_cooldown_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-ab36d51d4f60</t>
+          <t>d1-final-8fdd3599890f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig8_veto_cooldown_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/Fig8_veto_cooldown_data.xlsx
@@ -444,7 +444,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
